--- a/项目素材文件/完整普鲁士策划案/国策效果.xlsx
+++ b/项目素材文件/完整普鲁士策划案/国策效果.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\19413\Documents\Paradox Interactive\Hearts of Iron IV\mod\完整普鲁士策划案\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SteamLibrary\steamapps\workshop\content\394360\3489559287\项目素材文件\完整普鲁士策划案\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E48780A-325E-4C78-B4F6-A419DAB6A3DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D33472E-AFA5-4CEF-86FD-D84F9B661396}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="89">
   <si>
     <t>最后任期</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -311,10 +311,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>时间来到1936.4.15自动跳过</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>开启后续国策确定玩家选举立场，封锁准备国策</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -380,6 +376,10 @@
   </si>
   <si>
     <t>社民党和民主党支持率+10%（就是恶心你），添加选举民族精神</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>时间来到1936.7.30自动跳过</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -746,7 +746,7 @@
         <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -766,7 +766,7 @@
         <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E3" t="s">
         <v>6</v>
@@ -786,7 +786,7 @@
         <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E4" t="s">
         <v>12</v>
@@ -806,7 +806,7 @@
         <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E5" t="s">
         <v>15</v>
@@ -826,10 +826,10 @@
         <v>23</v>
       </c>
       <c r="D6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E6" t="s">
         <v>82</v>
-      </c>
-      <c r="E6" t="s">
-        <v>83</v>
       </c>
       <c r="F6" t="s">
         <v>24</v>
@@ -846,13 +846,13 @@
         <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E7" t="s">
         <v>26</v>
       </c>
       <c r="F7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -866,13 +866,13 @@
         <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E8" t="s">
         <v>28</v>
       </c>
       <c r="F8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -883,16 +883,16 @@
         <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>88</v>
       </c>
       <c r="D9" t="s">
         <v>19</v>
       </c>
       <c r="E9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -906,13 +906,13 @@
         <v>63</v>
       </c>
       <c r="D10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E10" t="s">
         <v>34</v>
       </c>
       <c r="F10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -926,13 +926,13 @@
         <v>63</v>
       </c>
       <c r="D11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E11" t="s">
         <v>35</v>
       </c>
       <c r="F11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -946,13 +946,13 @@
         <v>63</v>
       </c>
       <c r="D12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E12" t="s">
         <v>36</v>
       </c>
       <c r="F12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -966,7 +966,7 @@
         <v>40</v>
       </c>
       <c r="D13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E13" t="s">
         <v>43</v>
@@ -986,7 +986,7 @@
         <v>41</v>
       </c>
       <c r="D14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E14" t="s">
         <v>45</v>
@@ -1006,7 +1006,7 @@
         <v>42</v>
       </c>
       <c r="D15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E15" t="s">
         <v>46</v>
@@ -1026,7 +1026,7 @@
         <v>49</v>
       </c>
       <c r="D16" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E16" t="s">
         <v>50</v>
@@ -1046,7 +1046,7 @@
         <v>49</v>
       </c>
       <c r="D17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E17" t="s">
         <v>51</v>
@@ -1066,7 +1066,7 @@
         <v>53</v>
       </c>
       <c r="D18" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E18" t="s">
         <v>64</v>
@@ -1086,7 +1086,7 @@
         <v>53</v>
       </c>
       <c r="D19" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E19" t="s">
         <v>65</v>
@@ -1106,7 +1106,7 @@
         <v>60</v>
       </c>
       <c r="D20" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E20" t="s">
         <v>66</v>
@@ -1126,7 +1126,7 @@
         <v>61</v>
       </c>
       <c r="D21" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E21" t="s">
         <v>67</v>
@@ -1143,47 +1143,50 @@
         <v>19</v>
       </c>
       <c r="C22" t="s">
-        <v>71</v>
+        <v>31</v>
       </c>
       <c r="D22" t="s">
         <v>19</v>
       </c>
       <c r="E22" t="s">
+        <v>74</v>
+      </c>
+      <c r="F22" t="s">
         <v>75</v>
-      </c>
-      <c r="F22" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B23">
         <v>35</v>
       </c>
       <c r="C23" t="s">
+        <v>77</v>
+      </c>
+      <c r="D23" t="s">
+        <v>81</v>
+      </c>
+      <c r="E23" t="s">
         <v>78</v>
       </c>
-      <c r="D23" t="s">
-        <v>82</v>
-      </c>
-      <c r="E23" t="s">
-        <v>79</v>
-      </c>
       <c r="F23" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B24">
         <v>35</v>
       </c>
       <c r="C24" t="s">
-        <v>81</v>
+        <v>80</v>
+      </c>
+      <c r="D24" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
